--- a/GalernaDsp.xlsx
+++ b/GalernaDsp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cgute09684\kicad-wk\GalernaDsp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF1750B0-B336-48EB-826E-3B8EB7D35453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0F7FD0C-0D8F-4696-B043-BB9EFD4ED199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1870" yWindow="680" windowWidth="28800" windowHeight="15410" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="12732" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GalernaDsp" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="197">
   <si>
     <t>Reference</t>
   </si>
@@ -616,6 +616,9 @@
   </si>
   <si>
     <t>R1,R34,R27,R28</t>
+  </si>
+  <si>
+    <t>C11702</t>
   </si>
 </sst>
 </file>
@@ -795,12 +798,12 @@
   <cols>
     <col min="1" max="1" width="29.08984375" customWidth="1"/>
     <col min="2" max="2" width="4.08984375" customWidth="1"/>
-    <col min="3" max="3" width="28.81640625" customWidth="1"/>
+    <col min="3" max="3" width="25.54296875" customWidth="1"/>
     <col min="4" max="4" width="5.1796875" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="16.26953125" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="17" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="35.7265625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="296.1796875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="24.90625" customWidth="1"/>
+    <col min="8" max="8" width="20.08984375" customWidth="1"/>
     <col min="9" max="10" width="14.453125" customWidth="1"/>
     <col min="11" max="11" width="15.36328125" customWidth="1"/>
     <col min="12" max="12" width="17.7265625" customWidth="1"/>
@@ -1435,6 +1438,9 @@
       </c>
       <c r="H30" t="s">
         <v>20</v>
+      </c>
+      <c r="I30" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
